--- a/utils/monday_sprint_sprint_2026-03.xlsx
+++ b/utils/monday_sprint_sprint_2026-03.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="429">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,159 +87,159 @@
     <t>13/08/2025</t>
   </si>
   <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>35179</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Inserir dados para relatório do Setor de Desenvolvimento de Negócios</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>26937</t>
+  </si>
+  <si>
+    <t>BI Ronda - necessidade de implementação</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>34078</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Lentidão movimentação setorial</t>
+  </si>
+  <si>
+    <t>29536</t>
+  </si>
+  <si>
+    <t>Ajuste do sistema de impressão de formulários</t>
+  </si>
+  <si>
+    <t>34674</t>
+  </si>
+  <si>
+    <t>Planilha de Vendas</t>
+  </si>
+  <si>
+    <t>35694</t>
+  </si>
+  <si>
+    <t>Fluxo Padrão CDM</t>
+  </si>
+  <si>
+    <t>Bom dia Necessitamos a criação de um fluxo no padrão antigo, sem a necessidade do setor 500 pois o mesmo já nasce pronto. Somente os setores abaixo: 502 504 grato</t>
+  </si>
+  <si>
+    <t>Rafael Tamanini</t>
+  </si>
+  <si>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>35675</t>
+  </si>
+  <si>
+    <t>SERIAL NUMBER</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>35665</t>
+  </si>
+  <si>
+    <t>APONTAMNETO LINHAS UPR - ADEQUAÇÕES PARA LINHA FHASE FOUR</t>
+  </si>
+  <si>
+    <t>35660</t>
+  </si>
+  <si>
+    <t>Qliksense - Análise de Ofertas Comercial - Dúvida</t>
+  </si>
+  <si>
+    <t>Bom dia! Na tela de análise de ofertas comercial no qliksense, eu notei que os valores de Modelo/Dispositivo do filtro "Ofertas" não faz parte dos dados da tabela. Já para o filtro "Vendas", ocorre normalmente. Poderia por favor, ajustar para que o filtro de "Ofertas" também busque os valores de mod</t>
+  </si>
+  <si>
+    <t>Fernando Reinert</t>
+  </si>
+  <si>
+    <t>10/12/2025</t>
+  </si>
+  <si>
+    <t>35656</t>
+  </si>
+  <si>
+    <t>SISTEMA INVOICE // NOVA ABA OBSERVAÇÕES PROFORMA</t>
+  </si>
+  <si>
+    <t>35654</t>
+  </si>
+  <si>
+    <t>Coluna de NF - Relatório Serv. Terceiros</t>
+  </si>
+  <si>
+    <t>Boa tarde, No relatório gerado em excel sobre o envio de peças para serviço com terceiros a coluna com a informação da Nota Fiscal não está aparecendo. Favor incluir a coluna de NF tanto do envio quanto do retorno. Att,</t>
+  </si>
+  <si>
+    <t>Samuel Garcia</t>
+  </si>
+  <si>
+    <t>09/12/2025</t>
+  </si>
+  <si>
+    <t>35643</t>
+  </si>
+  <si>
+    <t>PERFEORMACE CABINES ESCARFAGEM REB 3</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>35638</t>
+  </si>
+  <si>
+    <t>IROG JATOS GANCHEIRAS +JATOS DIRIGIDO 1 E 2</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos avaliar aplicação irog com ênfase nos apontamentos dos jatos ultimo dia consta 17/11 e estamos apontando diariamente, verificar também coluna estado de fabricação, hoje é apontado estado da peça. Qualquer duvida a disposição;</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
     <t>10/03/2026</t>
   </si>
   <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>35179</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Inserir dados para relatório do Setor de Desenvolvimento de Negócios</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>26937</t>
-  </si>
-  <si>
-    <t>BI Ronda - necessidade de implementação</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>34078</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Lentidão movimentação setorial</t>
-  </si>
-  <si>
-    <t>29536</t>
-  </si>
-  <si>
-    <t>Ajuste do sistema de impressão de formulários</t>
-  </si>
-  <si>
-    <t>34674</t>
-  </si>
-  <si>
-    <t>Planilha de Vendas</t>
-  </si>
-  <si>
-    <t>35694</t>
-  </si>
-  <si>
-    <t>Fluxo Padrão CDM</t>
-  </si>
-  <si>
-    <t>Bom dia Necessitamos a criação de um fluxo no padrão antigo, sem a necessidade do setor 500 pois o mesmo já nasce pronto. Somente os setores abaixo: 502 504 grato</t>
-  </si>
-  <si>
-    <t>Rafael Tamanini</t>
-  </si>
-  <si>
-    <t>12/12/2025</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>35675</t>
-  </si>
-  <si>
-    <t>SERIAL NUMBER</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>35665</t>
-  </si>
-  <si>
-    <t>APONTAMNETO LINHAS UPR - ADEQUAÇÕES PARA LINHA FHASE FOUR</t>
-  </si>
-  <si>
-    <t>35660</t>
-  </si>
-  <si>
-    <t>Qliksense - Análise de Ofertas Comercial - Dúvida</t>
-  </si>
-  <si>
-    <t>Bom dia! Na tela de análise de ofertas comercial no qliksense, eu notei que os valores de Modelo/Dispositivo do filtro "Ofertas" não faz parte dos dados da tabela. Já para o filtro "Vendas", ocorre normalmente. Poderia por favor, ajustar para que o filtro de "Ofertas" também busque os valores de mod</t>
-  </si>
-  <si>
-    <t>Fernando Reinert</t>
-  </si>
-  <si>
-    <t>10/12/2025</t>
-  </si>
-  <si>
-    <t>35656</t>
-  </si>
-  <si>
-    <t>SISTEMA INVOICE // NOVA ABA OBSERVAÇÕES PROFORMA</t>
-  </si>
-  <si>
-    <t>35654</t>
-  </si>
-  <si>
-    <t>Coluna de NF - Relatório Serv. Terceiros</t>
-  </si>
-  <si>
-    <t>Boa tarde, No relatório gerado em excel sobre o envio de peças para serviço com terceiros a coluna com a informação da Nota Fiscal não está aparecendo. Favor incluir a coluna de NF tanto do envio quanto do retorno. Att,</t>
-  </si>
-  <si>
-    <t>Samuel Garcia</t>
-  </si>
-  <si>
-    <t>09/12/2025</t>
-  </si>
-  <si>
-    <t>35643</t>
-  </si>
-  <si>
-    <t>PERFEORMACE CABINES ESCARFAGEM REB 3</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>35638</t>
-  </si>
-  <si>
-    <t>IROG JATOS GANCHEIRAS +JATOS DIRIGIDO 1 E 2</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos avaliar aplicação irog com ênfase nos apontamentos dos jatos ultimo dia consta 17/11 e estamos apontando diariamente, verificar também coluna estado de fabricação, hoje é apontado estado da peça. Qualquer duvida a disposição;</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>15/03/2026</t>
-  </si>
-  <si>
     <t>35631</t>
   </si>
   <si>
@@ -348,7 +348,7 @@
     <t>02/12/2025</t>
   </si>
   <si>
-    <t>25/02/2026</t>
+    <t>20/02/2026</t>
   </si>
   <si>
     <t>Registro de Fechamento USE</t>
@@ -399,7 +399,7 @@
     <t>Bom dia, Estou fazendo a última verificação no novo sistema do Tratamento Térmico e vi que está faltando a parte de pesquisa de bloco de prova, conseguimos adicionar essa funcionalidade de pesquisa de bloco no novo sistema? Imagem da localização no menu onde é feita a pesquisa de blocos abaixo; Outr</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>35518</t>
@@ -408,9 +408,6 @@
     <t>TEMPOS PADRÕES DE ACABAMENTO</t>
   </si>
   <si>
-    <t>Bom dia, Favor correlacionar os tempos totais que estão no roteiro na coluna "Tempo Planejado" com os dados da planilha anexa, realizar a divisão no sistema que controla os tempos das atividades complementares. A planilha anexa separa os tempos por liga, favor verificarem se é possível criar essa re</t>
-  </si>
-  <si>
     <t>35514</t>
   </si>
   <si>
@@ -444,12 +441,6 @@
     <t>Trava na medição de H2</t>
   </si>
   <si>
-    <t xml:space="preserve">Bom dia, Ano passado foi criado o campo de registro para a medição de H2 no sistema de corridas, conforme imagem abaixo. Para melhorar os nossos registros, solicitamos criar uma trava no encerramento da corrida, caso o campo não estiver preenchido e for uma peça crítica que necessita dessa medição. </t>
-  </si>
-  <si>
-    <t>Barbara Braatz Vetter</t>
-  </si>
-  <si>
     <t>33651</t>
   </si>
   <si>
@@ -465,9 +456,6 @@
     <t>21/08/2025</t>
   </si>
   <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
     <t>33331</t>
   </si>
   <si>
@@ -534,9 +522,6 @@
     <t>Boa tarde! Gostaria de solicitar uma melhoria no sistema de pré-lista de materiais. Atualmente, o código de local diferencia os prédios (ex.: 01, 02, etc.). Como nossa Central de Químicos é restrita a apenas um colaborador, precisamos implementar uma trava no momento da requisição, permitindo que ap</t>
   </si>
   <si>
-    <t>26/02/2026</t>
-  </si>
-  <si>
     <t>35448</t>
   </si>
   <si>
@@ -600,6 +585,9 @@
     <t>20/11/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>35362</t>
   </si>
   <si>
@@ -627,502 +615,502 @@
     <t>Gabriel Lucas Kertichka</t>
   </si>
   <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>34403</t>
+  </si>
+  <si>
+    <t>Adicionar opção de trocar observação - Paradas sem peça (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde, seria muito bom se desse para trocar a observação na hora de apontar as paradas: Já que por exemplo no setor 1504 - Corte e Escarfa a gente aponta a Linha 1 e a Linha 2 e colocamos na observação quando apontamos produção, mas as paradas não dá, então na hora de extrair não tem como difere</t>
+  </si>
+  <si>
+    <t>Maria Eduarda Santos</t>
+  </si>
+  <si>
+    <t>29/09/2025</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>35668</t>
+  </si>
+  <si>
+    <t>Correção Procedimento FQA no Setor 540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde! Favor verificar erro de geração de demanda de procedimento pré-produtivo "FQA" no setor 540: Os itens destacados na imagem acima, tanto no saldo do setor quanto do relatório, estão como demanda de procedimento "FQA", mas nem possuem o setor no fluxo de pré-produtivo. Favor verificar este </t>
+  </si>
+  <si>
+    <t>Sergio Schmidt</t>
+  </si>
+  <si>
+    <t>34931</t>
+  </si>
+  <si>
+    <t>Corrigir Cálculo do Custo de Bloqueios</t>
+  </si>
+  <si>
+    <t>Boa tarde Sandro. Código Descrição Matéria Prima 100579 SUCATA BLOQUEIO EA-16001 CF3 100587 SUCATA BLOQUEIO EA-16002 CF3M 100722 SUCATA BLOQUEIO EA-16007 CA6NM 100922 SUCATA BLOQUEIO EA-16019 102467 SUCATA BLOQUEIO EA-16020</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>27/10/2025</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>32989</t>
+  </si>
+  <si>
+    <t>IROG Tratamento Térmico no BI</t>
+  </si>
+  <si>
+    <t>Bom dia, Foi conversado que, com as informações presentes hoje no sistema (disponibilidade, performance e qualidade), pode-se iniciar a implantação do IROG no BI. Em paralelo, o time da TI irá conduzir as melhorias pontuadas. Edson informou que o BI e melhorias serão atendidos em um mesmo chamado; 1</t>
+  </si>
+  <si>
+    <t>18/07/2025</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>32996</t>
+  </si>
+  <si>
+    <t>Implementação do Checklist no sistema de Tratamento Térmico</t>
+  </si>
+  <si>
+    <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
+  </si>
+  <si>
+    <t>35097</t>
+  </si>
+  <si>
+    <t>Mapeamento Digital</t>
+  </si>
+  <si>
+    <t>Boa tarde! Toda vez que estou revisando um mapeamento no sistema digital, e crio uma cavidade durante a revisão, apesar de colocar ela como "menor", quando eu concluo e imprimo o mapeamento revisado para conferir, este campo sempre fica em branco na última cavidade criada na revisão. Aí eu tenho que</t>
+  </si>
+  <si>
+    <t>04/11/2025</t>
+  </si>
+  <si>
+    <t>33965</t>
+  </si>
+  <si>
+    <t>Apontamento de moldes Carrossel - Homologação</t>
+  </si>
+  <si>
+    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>05/09/2025</t>
+  </si>
+  <si>
+    <t>24641</t>
+  </si>
+  <si>
+    <t>Cálculo de Horas para o BI por Macro área - Revisar a fórmula do cálculo de em todas as macro áreas (copy) (copy) (copy)</t>
+  </si>
+  <si>
+    <t>35130</t>
+  </si>
+  <si>
+    <t>Correções layout aplicação de faseamento de vendas</t>
+  </si>
+  <si>
+    <t>35503</t>
+  </si>
+  <si>
+    <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na reunião realizada em 02/10/2025, foi discutido o tema apropriação do custeio. Estiveram presentes: Rafael Pereira, Paulo Cruz e Alexandre Longo. Como já existiam dois chamados1 abertos, as tarefas foram inicialmente vinculadas a eles. Porém, com a evolução das demandas, ficou acordada a abertura </t>
+  </si>
+  <si>
+    <t>Alexandre Longo</t>
+  </si>
+  <si>
+    <t>Melhoria Sistema de Custeio - Materiais Secundários</t>
+  </si>
+  <si>
+    <t>30903</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Controle do status por declaração</t>
+  </si>
+  <si>
+    <t>Melhoria Sistema de Custeio - INSERTOS</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Fundição - subáreas</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Cadastro de cliente</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>Calculo do custo de embalagens</t>
+  </si>
+  <si>
+    <t>34073</t>
+  </si>
+  <si>
+    <t>Callback em aplicações WEB</t>
+  </si>
+  <si>
+    <t>CRM - Nova carga inicial de oportunidades</t>
+  </si>
+  <si>
+    <t>19909</t>
+  </si>
+  <si>
+    <t>Registro de pintura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>CRM - Atualizar IDERP nos registros já existentes (copy)</t>
+  </si>
+  <si>
+    <t>32677</t>
+  </si>
+  <si>
+    <t>PDI - Fixar colunas de identificação das cotas (copy)</t>
+  </si>
+  <si>
+    <t>CRM - Produtos não estão não estão disponibilizado descrição (copy)</t>
+  </si>
+  <si>
+    <t>CRM - Nova Carga de clientes (copy)</t>
+  </si>
+  <si>
+    <t>CRM - Testes unitários com usuário (oportunidade) (copy)</t>
+  </si>
+  <si>
+    <t>PDI - Inspeção - Cotas informadas. (copy)</t>
+  </si>
+  <si>
+    <t>33048</t>
+  </si>
+  <si>
+    <t>Custos FTF (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde Srs., Precisamos automatizar um levantamento de custo de FTF por setor. A ideia é ter listado as operações trazendo o custo previsto de FTF e horas previstas de FTF de todos os modelos faturados do mês. Em anexo o Excel do exemplo de informação que precisa ser listada. Qualquer dúvida, est</t>
+  </si>
+  <si>
+    <t>22/07/2025</t>
+  </si>
+  <si>
+    <t>Siga - Consulta Sequencia (Alt c) (copy)</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>Melhorias APS (copy)</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>35434</t>
+  </si>
+  <si>
+    <t>REVISÃO E CRIAÇÃO DE NOVOS FLUXOS (copy)</t>
+  </si>
+  <si>
+    <t>33509</t>
+  </si>
+  <si>
+    <t>Melhoria nas informações da FTF/ OFERTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Flávio, e demais, Além do chamado anexo, gostaríamos de implantar outra melhoria no sistema de FTFs, conforme segue: 1ºSolicitação: Incluir nas FTFs a informação de vida útil orçada do modelo (quantidade de peças que o modelo poderá fabricar), junto com as demais informações como material, </t>
+  </si>
+  <si>
+    <t>Pierro Conrrad da Silva</t>
+  </si>
+  <si>
+    <t>14/08/2025</t>
+  </si>
+  <si>
+    <t>35318</t>
+  </si>
+  <si>
+    <t>Elaboração de um sistema de atividades para o laboratorio Químico (copy)</t>
+  </si>
+  <si>
+    <t>35423</t>
+  </si>
+  <si>
+    <t>Sistema de programação das moldagens - REUNIÃO (copy)</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos fazer uma alteração no sistema de programação das moldagens, como podemos proceder? Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Jackson Souza</t>
+  </si>
+  <si>
+    <t>32037</t>
+  </si>
+  <si>
+    <t>BI ajustagem (copy)</t>
+  </si>
+  <si>
+    <t>34427</t>
+  </si>
+  <si>
+    <t>ETFIC - Analise (copy)</t>
+  </si>
+  <si>
+    <t>33271</t>
+  </si>
+  <si>
+    <t>Alinhamento dos cálculos de disponibilidade</t>
+  </si>
+  <si>
+    <t>33588</t>
+  </si>
+  <si>
+    <t>Indicador Cobertura de Estoques - Gerar Tabela (copy)</t>
+  </si>
+  <si>
+    <t>10779597074</t>
+  </si>
+  <si>
+    <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
+  </si>
+  <si>
+    <t>31270</t>
+  </si>
+  <si>
+    <t>MELHORIAS FLUXO 109 REVISÕES</t>
+  </si>
+  <si>
+    <t>35067</t>
+  </si>
+  <si>
+    <t>Erro IROG acabamento (copy)</t>
+  </si>
+  <si>
+    <t>Bom dia, Esta apresentando um erro no rateio de metas do IROG acabamento. At.te.,</t>
+  </si>
+  <si>
+    <t>Carlos Correia</t>
+  </si>
+  <si>
+    <t>34651</t>
+  </si>
+  <si>
+    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
+  </si>
+  <si>
+    <t>33191</t>
+  </si>
+  <si>
+    <t>Ticket - Programação</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>34921</t>
+  </si>
+  <si>
+    <t>HORIMETRO MANIULADORES (copy)</t>
+  </si>
+  <si>
+    <t>35206</t>
+  </si>
+  <si>
+    <t>Alterações nas etiquetas de moldagem (copy)</t>
+  </si>
+  <si>
+    <t>Boa Tarde! Segue abaixo as alterações necessárias para impressão das etiquetas de moldagem e cartão de vazamento. Ø Imprimir duas ou mais sequencias quando necessário Ø Imprimir duas cópias da etiqueta de moldagem Ø Não se faz necessário a impressão da etiqueta de moldagem ULE no momento. Att,</t>
+  </si>
+  <si>
+    <t>Luiz Ricardo Roedel</t>
+  </si>
+  <si>
+    <t>11/11/2025</t>
+  </si>
+  <si>
+    <t>33387</t>
+  </si>
+  <si>
+    <t>HORIMETRO MANIPULADORES (copy)</t>
+  </si>
+  <si>
+    <t>Bom dia, A um tempo atrás decidimos não ter os o apontamento do Horimetro dos manipuladores obrigatório, mas não está atendendo nossa realidade, vamos voltar atrás e manter ele obrigatório. Peso para que entre em contato @Maciel Nolli, para alinharmos certinho o que será feito. Temos um chamado cons</t>
+  </si>
+  <si>
+    <t>08/08/2025</t>
+  </si>
+  <si>
+    <t>34171</t>
+  </si>
+  <si>
+    <t>Contagem Proformas (copy)</t>
+  </si>
+  <si>
+    <t>35272</t>
+  </si>
+  <si>
+    <t>Contagem de Inventário (copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezados, Nos dias 05 e 06 de janeiro/2026 a Altona fará inventário de produtos em processo, identificando a quantidade de sequencias por setor. O sistema deverá possibilitar anexar foto da peça. Para tal funcionalidade, é necessária a construção de uma interface no sistema de WMS, com base na tela </t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>14/11/2025</t>
+  </si>
+  <si>
+    <t>35081</t>
+  </si>
+  <si>
+    <t>SUGESTÃO PARA MELHORIA NA H5000 (copy)</t>
+  </si>
+  <si>
+    <t>Bom dia, tudo certo? Gostaria de fazer uma sugestão de melhoria na H5000 com relação ao preenchimento da carta CEP e C3M. * Atualmente 1° - Atualmente o preenchimento desses dois arquivos são feitos manualmente, imprimimos o arquivo de excell para o operador e ele faz o preenchimento de forma manual</t>
+  </si>
+  <si>
+    <t>Wangadner Maycoll do Nascimento Costa</t>
+  </si>
+  <si>
+    <t>35257</t>
+  </si>
+  <si>
+    <t>Integração do mapeamento digital com sistema do PCP (copy)</t>
+  </si>
+  <si>
+    <t>34029</t>
+  </si>
+  <si>
+    <t>Nota técnica 2025.002 - Alteração no XML da nota</t>
+  </si>
+  <si>
+    <t>35127</t>
+  </si>
+  <si>
+    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
+  </si>
+  <si>
+    <t>33395</t>
+  </si>
+  <si>
+    <t>Ordens de Compra - Benner</t>
+  </si>
+  <si>
+    <t>35333</t>
+  </si>
+  <si>
+    <t>Solicitação de Implementação de Nova Funcionalidade no WMS – “Pré-Transferência Aciaria”</t>
+  </si>
+  <si>
+    <t>34599</t>
+  </si>
+  <si>
+    <t>Sistema de Embalagens - Relatório Requisição Embalagem por Sequência</t>
+  </si>
+  <si>
+    <t>Bom dia Sandro. Cristian me passou que o desenvolvimento do sistema para gestão de Embalagem está concluído. Ótima notícia. Desenvolver relatório conforme layout no anexo. Relatório será de período fechado de mês, após o fechamento do mês. Listar mesmo as requisições que não tenham vinculadas etique</t>
+  </si>
+  <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
+    <t>24746</t>
+  </si>
+  <si>
+    <t>Integração de faturamentos com eventos</t>
+  </si>
+  <si>
+    <t>28392</t>
+  </si>
+  <si>
+    <t>Notas de consignado - Medição NIMBI</t>
+  </si>
+  <si>
+    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>15/10/2024</t>
+  </si>
+  <si>
     <t>24/03/2026</t>
-  </si>
-  <si>
-    <t>34403</t>
-  </si>
-  <si>
-    <t>Adicionar opção de trocar observação - Paradas sem peça (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde, seria muito bom se desse para trocar a observação na hora de apontar as paradas: Já que por exemplo no setor 1504 - Corte e Escarfa a gente aponta a Linha 1 e a Linha 2 e colocamos na observação quando apontamos produção, mas as paradas não dá, então na hora de extrair não tem como difere</t>
-  </si>
-  <si>
-    <t>Maria Eduarda Santos</t>
-  </si>
-  <si>
-    <t>29/09/2025</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>35668</t>
-  </si>
-  <si>
-    <t>Correção Procedimento FQA no Setor 540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde! Favor verificar erro de geração de demanda de procedimento pré-produtivo "FQA" no setor 540: Os itens destacados na imagem acima, tanto no saldo do setor quanto do relatório, estão como demanda de procedimento "FQA", mas nem possuem o setor no fluxo de pré-produtivo. Favor verificar este </t>
-  </si>
-  <si>
-    <t>Sergio Schmidt</t>
-  </si>
-  <si>
-    <t>34931</t>
-  </si>
-  <si>
-    <t>Corrigir Cálculo do Custo de Bloqueios</t>
-  </si>
-  <si>
-    <t>Boa tarde Sandro. Código Descrição Matéria Prima 100579 SUCATA BLOQUEIO EA-16001 CF3 100587 SUCATA BLOQUEIO EA-16002 CF3M 100722 SUCATA BLOQUEIO EA-16007 CA6NM 100922 SUCATA BLOQUEIO EA-16019 102467 SUCATA BLOQUEIO EA-16020</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>27/10/2025</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>32989</t>
-  </si>
-  <si>
-    <t>IROG Tratamento Térmico no BI</t>
-  </si>
-  <si>
-    <t>Bom dia, Foi conversado que, com as informações presentes hoje no sistema (disponibilidade, performance e qualidade), pode-se iniciar a implantação do IROG no BI. Em paralelo, o time da TI irá conduzir as melhorias pontuadas. Edson informou que o BI e melhorias serão atendidos em um mesmo chamado; 1</t>
-  </si>
-  <si>
-    <t>18/07/2025</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>32996</t>
-  </si>
-  <si>
-    <t>Implementação do Checklist no sistema de Tratamento Térmico</t>
-  </si>
-  <si>
-    <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
-  </si>
-  <si>
-    <t>35097</t>
-  </si>
-  <si>
-    <t>Mapeamento Digital</t>
-  </si>
-  <si>
-    <t>Boa tarde! Toda vez que estou revisando um mapeamento no sistema digital, e crio uma cavidade durante a revisão, apesar de colocar ela como "menor", quando eu concluo e imprimo o mapeamento revisado para conferir, este campo sempre fica em branco na última cavidade criada na revisão. Aí eu tenho que</t>
-  </si>
-  <si>
-    <t>04/11/2025</t>
-  </si>
-  <si>
-    <t>33965</t>
-  </si>
-  <si>
-    <t>Apontamento de moldes Carrossel - Homologação</t>
-  </si>
-  <si>
-    <t>Boa tarde, Necessário criar no apontamento para carrossel, identificando a sequência e se são as partes superiores e Inferiores. Att.</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>24641</t>
-  </si>
-  <si>
-    <t>Cálculo de Horas para o BI por Macro área - Revisar a fórmula do cálculo de em todas as macro áreas (copy) (copy) (copy)</t>
-  </si>
-  <si>
-    <t>35130</t>
-  </si>
-  <si>
-    <t>Correções layout aplicação de faseamento de vendas</t>
-  </si>
-  <si>
-    <t>35503</t>
-  </si>
-  <si>
-    <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na reunião realizada em 02/10/2025, foi discutido o tema apropriação do custeio. Estiveram presentes: Rafael Pereira, Paulo Cruz e Alexandre Longo. Como já existiam dois chamados1 abertos, as tarefas foram inicialmente vinculadas a eles. Porém, com a evolução das demandas, ficou acordada a abertura </t>
-  </si>
-  <si>
-    <t>Alexandre Longo</t>
-  </si>
-  <si>
-    <t>Melhoria Sistema de Custeio - Materiais Secundários</t>
-  </si>
-  <si>
-    <t>30903</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Controle do status por declaração</t>
-  </si>
-  <si>
-    <t>Melhoria Sistema de Custeio - INSERTOS</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Fundição - subáreas</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Cadastro de cliente</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>Calculo do custo de embalagens</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>Callback em aplicações WEB</t>
-  </si>
-  <si>
-    <t>CRM - Nova carga inicial de oportunidades</t>
-  </si>
-  <si>
-    <t>19909</t>
-  </si>
-  <si>
-    <t>Registro de pintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>CRM - Atualizar IDERP nos registros já existentes (copy)</t>
-  </si>
-  <si>
-    <t>32677</t>
-  </si>
-  <si>
-    <t>PDI - Fixar colunas de identificação das cotas (copy)</t>
-  </si>
-  <si>
-    <t>CRM - Produtos não estão não estão disponibilizado descrição (copy)</t>
-  </si>
-  <si>
-    <t>CRM - Nova Carga de clientes (copy)</t>
-  </si>
-  <si>
-    <t>CRM - Testes unitários com usuário (oportunidade) (copy)</t>
-  </si>
-  <si>
-    <t>PDI - Inspeção - Cotas informadas. (copy)</t>
-  </si>
-  <si>
-    <t>33048</t>
-  </si>
-  <si>
-    <t>Custos FTF (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde Srs., Precisamos automatizar um levantamento de custo de FTF por setor. A ideia é ter listado as operações trazendo o custo previsto de FTF e horas previstas de FTF de todos os modelos faturados do mês. Em anexo o Excel do exemplo de informação que precisa ser listada. Qualquer dúvida, est</t>
-  </si>
-  <si>
-    <t>22/07/2025</t>
-  </si>
-  <si>
-    <t>Siga - Consulta Sequencia (Alt c) (copy)</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Melhorias APS (copy)</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
-  </si>
-  <si>
-    <t>10/02/2025</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>35434</t>
-  </si>
-  <si>
-    <t>REVISÃO E CRIAÇÃO DE NOVOS FLUXOS (copy)</t>
-  </si>
-  <si>
-    <t>33509</t>
-  </si>
-  <si>
-    <t>Melhoria nas informações da FTF/ OFERTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Flávio, e demais, Além do chamado anexo, gostaríamos de implantar outra melhoria no sistema de FTFs, conforme segue: 1ºSolicitação: Incluir nas FTFs a informação de vida útil orçada do modelo (quantidade de peças que o modelo poderá fabricar), junto com as demais informações como material, </t>
-  </si>
-  <si>
-    <t>Pierro Conrrad da Silva</t>
-  </si>
-  <si>
-    <t>14/08/2025</t>
-  </si>
-  <si>
-    <t>35318</t>
-  </si>
-  <si>
-    <t>Elaboração de um sistema de atividades para o laboratorio Químico (copy)</t>
-  </si>
-  <si>
-    <t>35423</t>
-  </si>
-  <si>
-    <t>Sistema de programação das moldagens - REUNIÃO (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos fazer uma alteração no sistema de programação das moldagens, como podemos proceder? Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Jackson Souza</t>
-  </si>
-  <si>
-    <t>32037</t>
-  </si>
-  <si>
-    <t>BI ajustagem (copy)</t>
-  </si>
-  <si>
-    <t>34427</t>
-  </si>
-  <si>
-    <t>ETFIC - Analise (copy)</t>
-  </si>
-  <si>
-    <t>33271</t>
-  </si>
-  <si>
-    <t>Alinhamento dos cálculos de disponibilidade</t>
-  </si>
-  <si>
-    <t>33588</t>
-  </si>
-  <si>
-    <t>Indicador Cobertura de Estoques - Gerar Tabela (copy)</t>
-  </si>
-  <si>
-    <t>10779597074</t>
-  </si>
-  <si>
-    <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
-  </si>
-  <si>
-    <t>31270</t>
-  </si>
-  <si>
-    <t>MELHORIAS FLUXO 109 REVISÕES</t>
-  </si>
-  <si>
-    <t>35067</t>
-  </si>
-  <si>
-    <t>Erro IROG acabamento (copy)</t>
-  </si>
-  <si>
-    <t>Bom dia, Esta apresentando um erro no rateio de metas do IROG acabamento. At.te.,</t>
-  </si>
-  <si>
-    <t>Carlos Correia</t>
-  </si>
-  <si>
-    <t>34651</t>
-  </si>
-  <si>
-    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
-  </si>
-  <si>
-    <t>33191</t>
-  </si>
-  <si>
-    <t>Ticket - Programação</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>34921</t>
-  </si>
-  <si>
-    <t>HORIMETRO MANIULADORES (copy)</t>
-  </si>
-  <si>
-    <t>35206</t>
-  </si>
-  <si>
-    <t>Alterações nas etiquetas de moldagem (copy)</t>
-  </si>
-  <si>
-    <t>Boa Tarde! Segue abaixo as alterações necessárias para impressão das etiquetas de moldagem e cartão de vazamento. Ø Imprimir duas ou mais sequencias quando necessário Ø Imprimir duas cópias da etiqueta de moldagem Ø Não se faz necessário a impressão da etiqueta de moldagem ULE no momento. Att,</t>
-  </si>
-  <si>
-    <t>Luiz Ricardo Roedel</t>
-  </si>
-  <si>
-    <t>11/11/2025</t>
-  </si>
-  <si>
-    <t>33387</t>
-  </si>
-  <si>
-    <t>HORIMETRO MANIPULADORES (copy)</t>
-  </si>
-  <si>
-    <t>Bom dia, A um tempo atrás decidimos não ter os o apontamento do Horimetro dos manipuladores obrigatório, mas não está atendendo nossa realidade, vamos voltar atrás e manter ele obrigatório. Peso para que entre em contato @Maciel Nolli, para alinharmos certinho o que será feito. Temos um chamado cons</t>
-  </si>
-  <si>
-    <t>08/08/2025</t>
-  </si>
-  <si>
-    <t>34171</t>
-  </si>
-  <si>
-    <t>Contagem Proformas (copy)</t>
-  </si>
-  <si>
-    <t>35272</t>
-  </si>
-  <si>
-    <t>Contagem de Inventário (copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prezados, Nos dias 05 e 06 de janeiro/2026 a Altona fará inventário de produtos em processo, identificando a quantidade de sequencias por setor. O sistema deverá possibilitar anexar foto da peça. Para tal funcionalidade, é necessária a construção de uma interface no sistema de WMS, com base na tela </t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>14/11/2025</t>
-  </si>
-  <si>
-    <t>35081</t>
-  </si>
-  <si>
-    <t>SUGESTÃO PARA MELHORIA NA H5000 (copy)</t>
-  </si>
-  <si>
-    <t>Bom dia, tudo certo? Gostaria de fazer uma sugestão de melhoria na H5000 com relação ao preenchimento da carta CEP e C3M. * Atualmente 1° - Atualmente o preenchimento desses dois arquivos são feitos manualmente, imprimimos o arquivo de excell para o operador e ele faz o preenchimento de forma manual</t>
-  </si>
-  <si>
-    <t>Wangadner Maycoll do Nascimento Costa</t>
-  </si>
-  <si>
-    <t>35257</t>
-  </si>
-  <si>
-    <t>Integração do mapeamento digital com sistema do PCP (copy)</t>
-  </si>
-  <si>
-    <t>34029</t>
-  </si>
-  <si>
-    <t>Nota técnica 2025.002 - Alteração no XML da nota</t>
-  </si>
-  <si>
-    <t>35127</t>
-  </si>
-  <si>
-    <t>Altona || Estoque IMOB 39551 - Entradas + Consumo Diferente do Saldo</t>
-  </si>
-  <si>
-    <t>33395</t>
-  </si>
-  <si>
-    <t>Ordens de Compra - Benner</t>
-  </si>
-  <si>
-    <t>35333</t>
-  </si>
-  <si>
-    <t>Solicitação de Implementação de Nova Funcionalidade no WMS – “Pré-Transferência Aciaria”</t>
-  </si>
-  <si>
-    <t>34599</t>
-  </si>
-  <si>
-    <t>Sistema de Embalagens - Relatório Requisição Embalagem por Sequência</t>
-  </si>
-  <si>
-    <t>Bom dia Sandro. Cristian me passou que o desenvolvimento do sistema para gestão de Embalagem está concluído. Ótima notícia. Desenvolver relatório conforme layout no anexo. Relatório será de período fechado de mês, após o fechamento do mês. Listar mesmo as requisições que não tenham vinculadas etique</t>
-  </si>
-  <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
-    <t>24746</t>
-  </si>
-  <si>
-    <t>Integração de faturamentos com eventos</t>
-  </si>
-  <si>
-    <t>28392</t>
-  </si>
-  <si>
-    <t>Notas de consignado - Medição NIMBI</t>
-  </si>
-  <si>
-    <t>Bom dia, Conforme reunião dia 10/10 com o Sandro, queremos solicitar uma alteração no sistema de consignados da empresa. Sobre os contratos de consignado será gerado uma ordem de compra, e dentro dessas ordens terão medições para os consumos dos consignados. Para verificar que a OC é referente a con</t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>15/10/2024</t>
-  </si>
-  <si>
-    <t>29/03/2026</t>
   </si>
   <si>
     <t>34720</t>
@@ -3119,25 +3107,25 @@
         <v>16</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>130</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>29</v>
@@ -3146,30 +3134,30 @@
         <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -3198,7 +3186,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -3210,22 +3198,22 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>48</v>
@@ -3234,42 +3222,42 @@
         <v>69</v>
       </c>
       <c r="M34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>144</v>
+        <v>29</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>29</v>
@@ -3278,15 +3266,15 @@
         <v>32</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -3298,25 +3286,25 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -3330,7 +3318,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3342,10 +3330,10 @@
         <v>29</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -3374,34 +3362,34 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>48</v>
@@ -3410,15 +3398,15 @@
         <v>32</v>
       </c>
       <c r="M38" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N38" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3430,10 +3418,10 @@
         <v>29</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>31</v>
@@ -3462,7 +3450,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3474,39 +3462,39 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3518,39 +3506,39 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M41" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N41" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3562,39 +3550,39 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N42" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3606,10 +3594,10 @@
         <v>29</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>31</v>
@@ -3638,7 +3626,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3650,10 +3638,10 @@
         <v>29</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3671,7 +3659,7 @@
         <v>29</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3682,7 +3670,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3694,10 +3682,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
@@ -3709,7 +3697,7 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>24</v>
@@ -3718,15 +3706,15 @@
         <v>25</v>
       </c>
       <c r="M45" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N45" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3738,22 +3726,22 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>48</v>
@@ -3762,15 +3750,15 @@
         <v>32</v>
       </c>
       <c r="M46" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N46" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3782,10 +3770,10 @@
         <v>29</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3814,7 +3802,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3826,25 +3814,25 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>32</v>
@@ -3853,12 +3841,12 @@
         <v>35</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3870,22 +3858,22 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>48</v>
@@ -3897,12 +3885,12 @@
         <v>35</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3914,25 +3902,25 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>32</v>
@@ -3941,12 +3929,12 @@
         <v>35</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3958,39 +3946,39 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -4002,16 +3990,16 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>22</v>
@@ -4034,7 +4022,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -4046,39 +4034,39 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -4090,39 +4078,39 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -4134,10 +4122,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -4149,7 +4137,7 @@
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>128</v>
@@ -4161,12 +4149,12 @@
         <v>35</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -4178,10 +4166,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -4193,7 +4181,7 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>128</v>
@@ -4205,12 +4193,12 @@
         <v>35</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -4222,22 +4210,22 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>128</v>
@@ -4249,12 +4237,12 @@
         <v>86</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -4266,22 +4254,22 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>29</v>
@@ -4293,12 +4281,12 @@
         <v>86</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -4310,10 +4298,10 @@
         <v>29</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>31</v>
@@ -4342,7 +4330,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4354,10 +4342,10 @@
         <v>29</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>31</v>
@@ -4386,7 +4374,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4398,39 +4386,39 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M61" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="M61" s="2" t="s">
+      <c r="N61" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4442,22 +4430,22 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>29</v>
@@ -4466,30 +4454,30 @@
         <v>25</v>
       </c>
       <c r="M62" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N62" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>31</v>
@@ -4518,7 +4506,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4530,22 +4518,22 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>29</v>
@@ -4554,15 +4542,15 @@
         <v>25</v>
       </c>
       <c r="M64" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N64" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4574,10 +4562,10 @@
         <v>29</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>31</v>
@@ -4595,7 +4583,7 @@
         <v>29</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>86</v>
@@ -4606,19 +4594,19 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>29</v>
@@ -4627,13 +4615,13 @@
         <v>20</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>29</v>
@@ -4642,15 +4630,15 @@
         <v>25</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4662,22 +4650,22 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>29</v>
@@ -4686,15 +4674,15 @@
         <v>25</v>
       </c>
       <c r="M67" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N67" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4706,10 +4694,10 @@
         <v>29</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4738,19 +4726,19 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>29</v>
@@ -4759,13 +4747,13 @@
         <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>29</v>
@@ -4774,15 +4762,15 @@
         <v>32</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4794,51 +4782,51 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>69</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>29</v>
@@ -4847,13 +4835,13 @@
         <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>29</v>
@@ -4862,15 +4850,15 @@
         <v>32</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4882,10 +4870,10 @@
         <v>29</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>31</v>
@@ -4914,19 +4902,19 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>29</v>
@@ -4935,13 +4923,13 @@
         <v>20</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>29</v>
@@ -4950,27 +4938,27 @@
         <v>32</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>29</v>
@@ -4979,13 +4967,13 @@
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>29</v>
@@ -4994,27 +4982,27 @@
         <v>32</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>29</v>
@@ -5023,13 +5011,13 @@
         <v>20</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>29</v>
@@ -5038,15 +5026,15 @@
         <v>32</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -5058,10 +5046,10 @@
         <v>29</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>31</v>
@@ -5090,7 +5078,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -5102,22 +5090,22 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>29</v>
@@ -5126,30 +5114,30 @@
         <v>25</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -5178,7 +5166,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -5190,25 +5178,25 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I79" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>32</v>
@@ -5217,12 +5205,12 @@
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -5234,10 +5222,10 @@
         <v>29</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>31</v>
@@ -5266,7 +5254,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -5278,22 +5266,22 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>48</v>
@@ -5310,7 +5298,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -5322,10 +5310,10 @@
         <v>29</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>31</v>
@@ -5354,7 +5342,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -5366,22 +5354,22 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>48</v>
@@ -5390,15 +5378,15 @@
         <v>32</v>
       </c>
       <c r="M83" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N83" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N83" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -5410,10 +5398,10 @@
         <v>29</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5442,22 +5430,22 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>31</v>
@@ -5486,7 +5474,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5498,10 +5486,10 @@
         <v>29</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>31</v>
@@ -5530,7 +5518,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5542,10 +5530,10 @@
         <v>29</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5574,7 +5562,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5586,10 +5574,10 @@
         <v>29</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>31</v>
@@ -5618,7 +5606,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5630,10 +5618,10 @@
         <v>29</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>31</v>
@@ -5662,7 +5650,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5671,42 +5659,42 @@
         <v>37</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>86</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5718,10 +5706,10 @@
         <v>29</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>31</v>
@@ -5750,7 +5738,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5762,10 +5750,10 @@
         <v>29</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>31</v>
@@ -5794,51 +5782,51 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5850,10 +5838,10 @@
         <v>29</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>31</v>
@@ -5882,7 +5870,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5894,22 +5882,22 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>48</v>
@@ -5921,12 +5909,12 @@
         <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5938,10 +5926,10 @@
         <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>31</v>
@@ -5953,7 +5941,7 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>48</v>
@@ -5970,7 +5958,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5982,10 +5970,10 @@
         <v>29</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>31</v>
@@ -6014,7 +6002,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -6026,22 +6014,22 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>48</v>
@@ -6053,12 +6041,12 @@
         <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -6070,22 +6058,22 @@
         <v>17</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>29</v>
@@ -6097,12 +6085,12 @@
         <v>86</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -6114,10 +6102,10 @@
         <v>29</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>31</v>
@@ -6146,7 +6134,7 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -6158,10 +6146,10 @@
         <v>29</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
@@ -6190,7 +6178,7 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -6202,10 +6190,10 @@
         <v>29</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>31</v>
@@ -6234,7 +6222,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>15</v>
@@ -6246,10 +6234,10 @@
         <v>29</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>20</v>
@@ -6278,7 +6266,7 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>15</v>
@@ -6290,10 +6278,10 @@
         <v>29</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>31</v>
@@ -6322,7 +6310,7 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>15</v>
@@ -6334,22 +6322,22 @@
         <v>17</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G105" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>29</v>
@@ -6361,27 +6349,27 @@
         <v>26</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>31</v>
@@ -6410,7 +6398,7 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>15</v>
@@ -6422,25 +6410,25 @@
         <v>17</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>25</v>
@@ -6449,12 +6437,12 @@
         <v>35</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>15</v>
@@ -6466,25 +6454,25 @@
         <v>17</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>32</v>
@@ -6493,12 +6481,12 @@
         <v>35</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -6510,10 +6498,10 @@
         <v>29</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>31</v>
@@ -6542,7 +6530,7 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>15</v>
@@ -6554,22 +6542,22 @@
         <v>17</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>29</v>
@@ -6578,30 +6566,30 @@
         <v>25</v>
       </c>
       <c r="M110" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N110" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N110" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>20</v>
@@ -6630,22 +6618,22 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>31</v>
@@ -6674,34 +6662,34 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>48</v>
@@ -6713,12 +6701,12 @@
         <v>26</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>15</v>
@@ -6730,39 +6718,39 @@
         <v>17</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>29</v>
+        <v>190</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>15</v>
@@ -6774,10 +6762,10 @@
         <v>29</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>20</v>
@@ -6795,7 +6783,7 @@
         <v>29</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M115" s="2" t="s">
         <v>35</v>
@@ -6806,7 +6794,7 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>15</v>
@@ -6818,10 +6806,10 @@
         <v>17</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>31</v>
@@ -6850,7 +6838,7 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>15</v>
@@ -6862,39 +6850,39 @@
         <v>17</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M117" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="N117" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N117" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>15</v>
@@ -6906,22 +6894,22 @@
         <v>17</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>48</v>
@@ -6933,12 +6921,12 @@
         <v>26</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>15</v>
@@ -6950,10 +6938,10 @@
         <v>29</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>31</v>
@@ -6971,7 +6959,7 @@
         <v>29</v>
       </c>
       <c r="L119" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>35</v>
@@ -6982,7 +6970,7 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>15</v>
@@ -6994,22 +6982,22 @@
         <v>17</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>48</v>
@@ -7021,12 +7009,12 @@
         <v>26</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>15</v>
@@ -7038,22 +7026,22 @@
         <v>17</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="I121" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>48</v>
@@ -7082,10 +7070,10 @@
         <v>29</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>31</v>
@@ -7106,7 +7094,7 @@
         <v>32</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>29</v>
@@ -7125,23 +7113,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7149,16 +7137,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7177,7 +7165,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -7198,7 +7186,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -7229,12 +7217,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B2">
         <v>121</v>
@@ -7258,25 +7246,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7293,13 +7281,13 @@
         <v>102</v>
       </c>
       <c r="G10" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7314,12 +7302,12 @@
         <v>86</v>
       </c>
       <c r="Q10">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E11">
         <v>13</v>
@@ -7331,7 +7319,7 @@
         <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="K11">
         <v>121</v>
@@ -7372,38 +7360,38 @@
         <v>35</v>
       </c>
       <c r="Q12">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="P13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q13">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -7417,7 +7405,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -7425,7 +7413,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -7433,7 +7421,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -7441,7 +7429,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -7452,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7460,142 +7448,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
